--- a/dist/成果/防治对象/测量表/360481002210102_光明村坎下詹家/沟道纵断面成果表_AFAE900128H00000ZACS004.xlsx
+++ b/dist/成果/防治对象/测量表/360481002210102_光明村坎下詹家/沟道纵断面成果表_AFAE900128H00000ZACS004.xlsx
@@ -822,7 +822,7 @@
         <v>21.783</v>
       </c>
       <c r="F12" s="22" t="n">
-        <v>22.08090393411384</v>
+        <v>22.0368206108947</v>
       </c>
       <c r="G12" s="23" t="n">
         <v>115.60818</v>
@@ -850,7 +850,7 @@
         <v>21.576</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>21.66452339089189</v>
+        <v>21.81657465867786</v>
       </c>
       <c r="G13" s="23" t="n">
         <v>115.608346</v>
@@ -878,7 +878,7 @@
         <v>21.36</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>21.54457975096733</v>
+        <v>21.80788934686092</v>
       </c>
       <c r="G14" s="23" t="n">
         <v>115.608469</v>
@@ -906,7 +906,7 @@
         <v>21.397</v>
       </c>
       <c r="F15" s="22" t="n">
-        <v>21.72128961261759</v>
+        <v>21.70375243116868</v>
       </c>
       <c r="G15" s="23" t="n">
         <v>115.608632</v>
@@ -934,7 +934,7 @@
         <v>21.575</v>
       </c>
       <c r="F16" s="22" t="n">
-        <v>21.67772206492827</v>
+        <v>21.84273252068987</v>
       </c>
       <c r="G16" s="23" t="n">
         <v>115.609007</v>
@@ -962,7 +962,7 @@
         <v>21.428</v>
       </c>
       <c r="F17" s="22" t="n">
-        <v>21.56736525270737</v>
+        <v>21.84215380472837</v>
       </c>
       <c r="G17" s="23" t="n">
         <v>115.609059</v>
@@ -990,7 +990,7 @@
         <v>21.381</v>
       </c>
       <c r="F18" s="22" t="n">
-        <v>21.52327659637132</v>
+        <v>21.42024923060436</v>
       </c>
       <c r="G18" s="23" t="n">
         <v>115.609369</v>
@@ -1018,7 +1018,7 @@
         <v>21.624</v>
       </c>
       <c r="F19" s="22" t="n">
-        <v>21.79388932065564</v>
+        <v>21.89794934008171</v>
       </c>
       <c r="G19" s="23" t="n">
         <v>115.609641</v>
@@ -1046,7 +1046,7 @@
         <v>21.81</v>
       </c>
       <c r="F20" s="22" t="n">
-        <v>21.94755114961257</v>
+        <v>22.14140867230702</v>
       </c>
       <c r="G20" s="23" t="n">
         <v>115.609828</v>
@@ -1074,7 +1074,7 @@
         <v>21.656</v>
       </c>
       <c r="F21" s="22" t="n">
-        <v>21.9142838178146</v>
+        <v>22.02767212647741</v>
       </c>
       <c r="G21" s="23" t="n">
         <v>115.610132</v>
@@ -1102,7 +1102,7 @@
         <v>21.471</v>
       </c>
       <c r="F22" s="22" t="n">
-        <v>21.78877032954406</v>
+        <v>21.72788229722934</v>
       </c>
       <c r="G22" s="23" t="n">
         <v>115.610371</v>
@@ -1130,7 +1130,7 @@
         <v>21.536</v>
       </c>
       <c r="F23" s="22" t="n">
-        <v>21.55686821739113</v>
+        <v>21.65400622736053</v>
       </c>
       <c r="G23" s="23" t="n">
         <v>115.610585</v>
@@ -1158,7 +1158,7 @@
         <v>21.435</v>
       </c>
       <c r="F24" s="22" t="n">
-        <v>21.72597388467936</v>
+        <v>21.65186641808504</v>
       </c>
       <c r="G24" s="23" t="n">
         <v>115.610789</v>
@@ -1186,7 +1186,7 @@
         <v>21.49</v>
       </c>
       <c r="F25" s="22" t="n">
-        <v>21.52418441661535</v>
+        <v>21.9187087776756</v>
       </c>
       <c r="G25" s="23" t="n">
         <v>115.611001</v>
@@ -1214,7 +1214,7 @@
         <v>21.566</v>
       </c>
       <c r="F26" s="22" t="n">
-        <v>21.68102956124048</v>
+        <v>21.77561855336607</v>
       </c>
       <c r="G26" s="23" t="n">
         <v>115.611252</v>
@@ -1242,7 +1242,7 @@
         <v>21.537</v>
       </c>
       <c r="F27" s="22" t="n">
-        <v>21.70521173111068</v>
+        <v>21.70754293452819</v>
       </c>
       <c r="G27" s="23" t="n">
         <v>115.611644</v>
@@ -1270,7 +1270,7 @@
         <v>21.466</v>
       </c>
       <c r="F28" s="22" t="n">
-        <v>21.6918246066876</v>
+        <v>21.59081976960251</v>
       </c>
       <c r="G28" s="23" t="n">
         <v>115.611977</v>
@@ -1298,7 +1298,7 @@
         <v>21.33</v>
       </c>
       <c r="F29" s="22" t="n">
-        <v>21.38292719249052</v>
+        <v>21.81933237695728</v>
       </c>
       <c r="G29" s="23" t="n">
         <v>115.612214</v>
@@ -1326,7 +1326,7 @@
         <v>21.401</v>
       </c>
       <c r="F30" s="22" t="n">
-        <v>21.78779452225662</v>
+        <v>21.51827491861603</v>
       </c>
       <c r="G30" s="23" t="n">
         <v>115.612446</v>
@@ -1354,7 +1354,7 @@
         <v>21.793</v>
       </c>
       <c r="F31" s="22" t="n">
-        <v>22.20112369515534</v>
+        <v>21.8132001370669</v>
       </c>
       <c r="G31" s="23" t="n">
         <v>115.612732</v>
@@ -1382,7 +1382,7 @@
         <v>21.477</v>
       </c>
       <c r="F32" s="22" t="n">
-        <v>22.151</v>
+        <v>21.63718158595698</v>
       </c>
       <c r="G32" s="23" t="n">
         <v>115.613033</v>
@@ -1410,7 +1410,7 @@
         <v>21.333</v>
       </c>
       <c r="F33" s="22" t="n">
-        <v>21.87206818955996</v>
+        <v>21.33589879895317</v>
       </c>
       <c r="G33" s="23" t="n">
         <v>115.613231</v>
@@ -1438,7 +1438,7 @@
         <v>21.225</v>
       </c>
       <c r="F34" s="22" t="n">
-        <v>21.85415969023838</v>
+        <v>21.70645380803644</v>
       </c>
       <c r="G34" s="23" t="n">
         <v>115.613437</v>
@@ -1466,7 +1466,7 @@
         <v>21.522</v>
       </c>
       <c r="F35" s="22" t="n">
-        <v>21.58594776253124</v>
+        <v>21.59765241074815</v>
       </c>
       <c r="G35" s="23" t="n">
         <v>115.613703</v>
@@ -1494,7 +1494,7 @@
         <v>21.671</v>
       </c>
       <c r="F36" s="22" t="n">
-        <v>21.73491276904942</v>
+        <v>22.15526207637019</v>
       </c>
       <c r="G36" s="23" t="n">
         <v>115.613784</v>
@@ -1522,7 +1522,7 @@
         <v>22.11</v>
       </c>
       <c r="F37" s="22" t="n">
-        <v>22.15290443007307</v>
+        <v>22.45746616581647</v>
       </c>
       <c r="G37" s="23" t="n">
         <v>115.613787</v>
@@ -1550,7 +1550,7 @@
         <v>22.116</v>
       </c>
       <c r="F38" s="22" t="n">
-        <v>22.39065834925675</v>
+        <v>22.171</v>
       </c>
       <c r="G38" s="23" t="n">
         <v>115.613796</v>
@@ -1606,7 +1606,7 @@
         <v>20.843</v>
       </c>
       <c r="F40" s="22" t="n">
-        <v>21.57362511884014</v>
+        <v>21.60433318403361</v>
       </c>
       <c r="G40" s="23" t="n">
         <v>115.613837</v>
@@ -1634,7 +1634,7 @@
         <v>21.614</v>
       </c>
       <c r="F41" s="22" t="n">
-        <v>21.68382575752895</v>
+        <v>21.91107875620656</v>
       </c>
       <c r="G41" s="23" t="n">
         <v>115.61384</v>
@@ -1718,7 +1718,7 @@
         <v>21.159</v>
       </c>
       <c r="F44" s="22" t="n">
-        <v>21.39701497129632</v>
+        <v>21.27164770706262</v>
       </c>
       <c r="G44" s="23" t="n">
         <v>115.613988</v>
@@ -1746,7 +1746,7 @@
         <v>20.964</v>
       </c>
       <c r="F45" s="22" t="n">
-        <v>21.35658015556781</v>
+        <v>21.12332578557234</v>
       </c>
       <c r="G45" s="23" t="n">
         <v>115.61398</v>
@@ -1774,7 +1774,7 @@
         <v>21.012</v>
       </c>
       <c r="F46" s="22" t="n">
-        <v>21.32099704653688</v>
+        <v>21.27600650689935</v>
       </c>
       <c r="G46" s="23" t="n">
         <v>115.614157</v>
@@ -1802,7 +1802,7 @@
         <v>20.77</v>
       </c>
       <c r="F47" s="22" t="n">
-        <v>21.18470730828008</v>
+        <v>20.80378701300313</v>
       </c>
       <c r="G47" s="23" t="n">
         <v>115.614339</v>
@@ -1830,7 +1830,7 @@
         <v>20.705</v>
       </c>
       <c r="F48" s="22" t="n">
-        <v>20.78641807270406</v>
+        <v>20.89797866187579</v>
       </c>
       <c r="G48" s="23" t="n">
         <v>115.614625</v>
@@ -1858,7 +1858,7 @@
         <v>20.048</v>
       </c>
       <c r="F49" s="22" t="n">
-        <v>20.42931656592428</v>
+        <v>20.50311980788178</v>
       </c>
       <c r="G49" s="23" t="n">
         <v>115.614776</v>
@@ -1886,7 +1886,7 @@
         <v>20.3</v>
       </c>
       <c r="F50" s="22" t="n">
-        <v>20.32026209025543</v>
+        <v>20.77889521405328</v>
       </c>
       <c r="G50" s="23" t="n">
         <v>115.614938</v>
@@ -1914,7 +1914,7 @@
         <v>20.08</v>
       </c>
       <c r="F51" s="22" t="n">
-        <v>20.22490679576383</v>
+        <v>20.43520689208041</v>
       </c>
       <c r="G51" s="23" t="n">
         <v>115.61502</v>
@@ -1942,7 +1942,7 @@
         <v>19.841</v>
       </c>
       <c r="F52" s="22" t="n">
-        <v>20.17099763065636</v>
+        <v>20.4118522774182</v>
       </c>
       <c r="G52" s="23" t="n">
         <v>115.615131</v>
@@ -1970,7 +1970,7 @@
         <v>20.089</v>
       </c>
       <c r="F53" s="22" t="n">
-        <v>20.26262763878969</v>
+        <v>20.09152254529637</v>
       </c>
       <c r="G53" s="23" t="n">
         <v>115.61525</v>
@@ -1998,7 +1998,7 @@
         <v>20.268</v>
       </c>
       <c r="F54" s="22" t="n">
-        <v>20.71318032160256</v>
+        <v>20.2801740626129</v>
       </c>
       <c r="G54" s="23" t="n">
         <v>115.615427</v>
@@ -2026,7 +2026,7 @@
         <v>20.179</v>
       </c>
       <c r="F55" s="22" t="n">
-        <v>20.23272554011821</v>
+        <v>20.38962572698889</v>
       </c>
       <c r="G55" s="23" t="n">
         <v>115.615561</v>
@@ -2054,7 +2054,7 @@
         <v>20.145</v>
       </c>
       <c r="F56" s="22" t="n">
-        <v>20.5156405458094</v>
+        <v>20.33609676246065</v>
       </c>
       <c r="G56" s="23" t="n">
         <v>115.615778</v>
@@ -2082,7 +2082,7 @@
         <v>20.38</v>
       </c>
       <c r="F57" s="22" t="n">
-        <v>20.44946404904886</v>
+        <v>20.58777734082513</v>
       </c>
       <c r="G57" s="23" t="n">
         <v>115.616015</v>
@@ -2110,7 +2110,7 @@
         <v>20.186</v>
       </c>
       <c r="F58" s="22" t="n">
-        <v>20.46284674971749</v>
+        <v>20.478</v>
       </c>
       <c r="G58" s="23" t="n">
         <v>115.616203</v>
@@ -2134,16 +2134,16 @@
     <mergeCell ref="D3:H3"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="D2:H2" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="D2:H2" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation sqref="B7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"85高程系,假定高程系"</formula1>
     </dataValidation>
-    <dataValidation sqref="D7:H7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="D7:H7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"水准仪／卷尺测量法,GNSS RTK测量法,全站仪法,三维激光扫描方法"</formula1>
     </dataValidation>
   </dataValidations>
